--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3334</v>
+        <v>3336</v>
       </c>
       <c r="Q2" t="n">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="R2" t="n">
-        <v>5049</v>
+        <v>5053</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>에센셜짐 헬스장&amp;PT 마곡점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>essential_gym_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>0507-1415-2641</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울특별시 강서구 공항대로 190 316~319호(마곡동, 푸리마타워)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>http://에센셜짐.shop</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>708</v>
+        <v>233</v>
       </c>
       <c r="Q3" t="n">
-        <v>235</v>
+        <v>713</v>
       </c>
       <c r="R3" t="n">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>1808375578</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/1808375578</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에센셜짐 헬스장&amp;PT 마곡점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>essential_gym_@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-2641</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 190 316~319호(마곡동, 푸리마타워)</t>
+          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://에센셜짐.shop</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>233</v>
+        <v>708</v>
       </c>
       <c r="Q4" t="n">
-        <v>713</v>
+        <v>232</v>
       </c>
       <c r="R4" t="n">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1808375578</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1808375578</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -906,10 +906,10 @@
         <v>366</v>
       </c>
       <c r="Q5" t="n">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="R5" t="n">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="R6" t="n">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1029,43 +1029,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 마곡 원그로브</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>goforit_20_@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1394-3687</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1080,17 +1076,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmjt3l5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2084897715</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084897715</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1131,39 +1123,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>운동으로우주정복PT</t>
+          <t>아이엠밸런스필라테스 마곡점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unujeong2023@naver.com</t>
+          <t>imbalancepilates@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-9365</t>
+          <t>0507-1416-0829</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙로 161-8 에이동 2층 201,202호</t>
+          <t>서울 강서구 마곡동로3길 26 랑데르2 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unujeong2023</t>
+          <t>https://pf.kakao.com/_fxhhtG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1173,18 +1165,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f6k6</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="n">
-        <v>313</v>
+        <v>71</v>
       </c>
       <c r="R8" t="n">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1432557076</t>
+          <t>71954376</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1432557076</t>
+          <t>https://m.place.naver.com/place/71954376</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,33 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 마곡 원그로브</t>
+          <t>바디채널 화곡2호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bodygymmm@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1399-3624</t>
+          <t>0507-1409-2606</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
+          <t>서울특별시 강서구 곰달래로 198 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/bodygymmm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1291,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>931</v>
+        <v>71</v>
       </c>
       <c r="Q9" t="n">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="R9" t="n">
-        <v>1067</v>
+        <v>371</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2038453115</t>
+          <t>1348945802</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038453115</t>
+          <t>https://m.place.naver.com/place/1348945802</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1323,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>자마이카 휘트니스 화곡점</t>
+          <t>피티하모니 강서구청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jamaicahwagok@naver.com</t>
+          <t>tuvasmedetruire0@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1309-9976</t>
+          <t>0507-1355-2365</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 161 대성빌딩</t>
+          <t>서울특별시 강서구 화곡로 339 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jamaicahwagok</t>
+          <t>https://blog.naver.com/tuvasmedetruire0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1385,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1246</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1870</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>3116</v>
+        <v>40</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>18394104</t>
+          <t>2082352683</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/18394104</t>
+          <t>https://m.place.naver.com/place/2082352683</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1417,39 +1409,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디채널 화곡점</t>
+          <t>껀바디 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodychannel04@naver.com</t>
+          <t>kkunbody@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-2035</t>
+          <t>0507-1329-8356</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
+          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannel04</t>
+          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1459,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>440</v>
+        <v>95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2194</v>
+        <v>269</v>
       </c>
       <c r="R11" t="n">
-        <v>2634</v>
+        <v>364</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1213490853</t>
+          <t>1200267493</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213490853</t>
+          <t>https://m.place.naver.com/place/1200267493</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3336</v>
+        <v>3366</v>
       </c>
       <c r="Q2" t="n">
-        <v>1717</v>
+        <v>1732</v>
       </c>
       <c r="R2" t="n">
-        <v>5053</v>
+        <v>5098</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에센셜짐 헬스장&amp;PT 마곡점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>essential_gym_@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1415-2641</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 190 316~319호(마곡동, 푸리마타워)</t>
+          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://에센셜짐.shop</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>233</v>
+        <v>705</v>
       </c>
       <c r="Q3" t="n">
-        <v>713</v>
+        <v>216</v>
       </c>
       <c r="R3" t="n">
-        <v>946</v>
+        <v>921</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1808375578</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1808375578</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,44 +752,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>1986피트니스 헬스PT 24시 가양점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>1986fitness0@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>0507-1314-5607</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>https://blog.naver.com/1986fitness0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>708</v>
+        <v>1633</v>
       </c>
       <c r="Q4" t="n">
-        <v>232</v>
+        <v>1185</v>
       </c>
       <c r="R4" t="n">
-        <v>940</v>
+        <v>2818</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>37769368</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/37769368</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="Q5" t="n">
-        <v>2131</v>
+        <v>2185</v>
       </c>
       <c r="R5" t="n">
-        <v>2497</v>
+        <v>2558</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바디프로짐 PT 헬스</t>
+          <t>에이블짐 신방화역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bodyprogym@naver.com</t>
+          <t>ablegym14@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1422-3752</t>
+          <t>0507-1411-7984</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 194 퀸즈파크12차 3층 301~309호 바디프로짐</t>
+          <t>서울특별시 강서구 방화대로 294 W타워 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DBLC48-PbhN/?igsh=Z2dqN3ViNXF3NzEy</t>
+          <t>https://blog.naver.com/ablegym14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1117</v>
+        <v>1468</v>
       </c>
       <c r="Q6" t="n">
-        <v>1786</v>
+        <v>549</v>
       </c>
       <c r="R6" t="n">
-        <v>2903</v>
+        <v>2017</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1945610411</t>
+          <t>1436688442</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945610411</t>
+          <t>https://m.place.naver.com/place/1436688442</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>바디채널 화곡점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>bodychannel04@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1314-2035</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://blog.naver.com/bodychannel04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>76</v>
+        <v>442</v>
       </c>
       <c r="Q7" t="n">
-        <v>211</v>
+        <v>2212</v>
       </c>
       <c r="R7" t="n">
-        <v>287</v>
+        <v>2654</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,55 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1213490853</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1213490853</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이엠밸런스필라테스 마곡점</t>
+          <t>버핏그라운드 PT 마곡 원그로브</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>imbalancepilates@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1416-0829</t>
+          <t>0507-1394-3687</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 강서구 마곡동로3길 26 랑데르2 4층</t>
+          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_fxhhtG</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1175,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f6k6</t>
+          <t>https://talk.naver.com/ct/wmjt3l5</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1189,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>71954376</t>
+          <t>2084897715</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/71954376</t>
+          <t>https://m.place.naver.com/place/2084897715</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디채널 화곡2호점</t>
+          <t>휘트니스피플 우먼 화곡역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodygymmm@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1409-2606</t>
+          <t>02-2602-3912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 곰달래로 198 2층</t>
+          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodygymmm</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>71</v>
+        <v>1307</v>
       </c>
       <c r="Q9" t="n">
-        <v>300</v>
+        <v>1495</v>
       </c>
       <c r="R9" t="n">
-        <v>371</v>
+        <v>2802</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1302,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1348945802</t>
+          <t>1818807982</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348945802</t>
+          <t>https://m.place.naver.com/place/1818807982</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피티하모니 강서구청점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tuvasmedetruire0@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-2365</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 339 5층</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tuvasmedetruire0</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>222</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>298</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2082352683</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082352683</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1414,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>껀바디 PT&amp;필라테스</t>
+          <t>바디채널 짐그라운드 등촌점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kkunbody@naver.com</t>
+          <t>bodychannel15@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1329-8356</t>
+          <t>0507-1397-8868</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
+          <t>서울특별시 강서구 공항대로 525 비원오피스텔 15층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
+          <t>https://www.bodychannel.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1455,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>95</v>
+        <v>454</v>
       </c>
       <c r="Q11" t="n">
-        <v>269</v>
+        <v>1928</v>
       </c>
       <c r="R11" t="n">
-        <v>364</v>
+        <v>2382</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1490,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1200267493</t>
+          <t>1857550136</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200267493</t>
+          <t>https://m.place.naver.com/place/1857550136</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 마곡나루지점</t>
+          <t>스마트짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym5@naver.com</t>
+          <t>smartgympt@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-8670-8894</t>
+          <t>0507-1428-4878</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
+          <t>부산 강서구 명지오션시티4로 69 2층 202호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym5</t>
+          <t>https://blog.naver.com/smartgympt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2vsm6z</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3366</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1732</v>
+        <v>47</v>
       </c>
       <c r="R2" t="n">
-        <v>5098</v>
+        <v>53</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1273553431</t>
+          <t>2064367886</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273553431</t>
+          <t>https://m.place.naver.com/place/2064367886</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,44 +662,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>에이블짐 마곡나루지점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>ablegym5@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>070-8670-8894</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>https://blog.naver.com/ablegym5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>705</v>
+        <v>3370</v>
       </c>
       <c r="Q3" t="n">
-        <v>216</v>
+        <v>1732</v>
       </c>
       <c r="R3" t="n">
-        <v>921</v>
+        <v>5102</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>1273553431</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/1273553431</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,44 +756,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 24시 가양점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1986fitness0@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-5607</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
+          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness0</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1633</v>
+        <v>705</v>
       </c>
       <c r="Q4" t="n">
-        <v>1185</v>
+        <v>218</v>
       </c>
       <c r="R4" t="n">
-        <v>2818</v>
+        <v>923</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37769368</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37769368</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전문 PT 헬스 바이브먼트</t>
+          <t>1986피트니스 헬스PT 24시 가양점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>vibement_magok@naver.com</t>
+          <t>1986fitness0@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1471-4007</t>
+          <t>0507-1314-5607</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 212 B동 4층 405호~ 407호</t>
+          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vibement_magok</t>
+          <t>https://blog.naver.com/1986fitness0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>373</v>
+        <v>1637</v>
       </c>
       <c r="Q5" t="n">
-        <v>2185</v>
+        <v>1186</v>
       </c>
       <c r="R5" t="n">
-        <v>2558</v>
+        <v>2823</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1814620278</t>
+          <t>37769368</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814620278</t>
+          <t>https://m.place.naver.com/place/37769368</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1022,41 +1026,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디채널 화곡점</t>
+          <t>바디프로짐 PT 헬스 가양점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodychannel04@naver.com</t>
+          <t>bodyprogym2_gayang@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1314-2035</t>
+          <t>0507-1391-7831</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
+          <t>서울특별시 강서구 화곡로68길 3 영스퀘어 7층 바디프로짐 가양점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannel04</t>
+          <t>https://www.instagram.com/bodyprogym2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>442</v>
+        <v>1046</v>
       </c>
       <c r="Q7" t="n">
-        <v>2212</v>
+        <v>997</v>
       </c>
       <c r="R7" t="n">
-        <v>2654</v>
+        <v>2043</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1213490853</t>
+          <t>1361992477</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213490853</t>
+          <t>https://m.place.naver.com/place/1361992477</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,38 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 마곡 원그로브</t>
+          <t>운동으로우주정복PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>unujeong2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1394-3687</t>
+          <t>0507-1341-9365</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
+          <t>서울특별시 강서구 마곡중앙로 161-8 에이동 2층 201,202호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/unujeong2023</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1174,17 +1174,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmjt3l5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>314</v>
       </c>
       <c r="R8" t="n">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2084897715</t>
+          <t>1432557076</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084897715</t>
+          <t>https://m.place.naver.com/place/1432557076</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1226,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 화곡역점</t>
+          <t>버핏그라운드 마곡 원그로브</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-2602-3912</t>
+          <t>0507-1399-3624</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
+          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1307</v>
+        <v>943</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495</v>
+        <v>143</v>
       </c>
       <c r="R9" t="n">
-        <v>2802</v>
+        <v>1086</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1818807982</t>
+          <t>2038453115</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1818807982</t>
+          <t>https://m.place.naver.com/place/2038453115</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>바디채널 화곡점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>bodychannel04@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1314-2035</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://blog.naver.com/bodychannel04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>76</v>
+        <v>442</v>
       </c>
       <c r="Q10" t="n">
-        <v>222</v>
+        <v>2212</v>
       </c>
       <c r="R10" t="n">
-        <v>298</v>
+        <v>2654</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1213490853</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1213490853</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1418,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디채널 짐그라운드 등촌점</t>
+          <t>버핏그라운드 PT 마곡 원그로브</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodychannel15@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1397-8868</t>
+          <t>0507-1394-3687</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 525 비원오피스텔 15층</t>
+          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.bodychannel.co.kr/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1460,13 +1464,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmjt3l5</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1483,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>454</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>1928</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2382</v>
+        <v>18</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1498,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1857550136</t>
+          <t>2084897715</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857550136</t>
+          <t>https://m.place.naver.com/place/2084897715</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 화곡역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02-2602-3912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fpeoplew1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1309</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1495</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2804</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1818807982</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1818807982</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스마트짐</t>
+          <t>에이블짐 마곡나루지점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>smartgympt@naver.com</t>
+          <t>ablegym5@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1428-4878</t>
+          <t>070-8670-8894</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 강서구 명지오션시티4로 69 2층 202호</t>
+          <t>서울 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/smartgympt</t>
+          <t>https://blog.naver.com/ablegym5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2vsm6z</t>
+          <t>https://talk.naver.com/ct/w4gb51</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>3370</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>1732</v>
       </c>
       <c r="R2" t="n">
-        <v>53</v>
+        <v>5102</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2064367886</t>
+          <t>1273553431</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064367886</t>
+          <t>https://m.place.naver.com/place/1273553431</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,52 +662,56 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 마곡나루지점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym5@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-8670-8894</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
+          <t>서울 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym5</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xo5w</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3370</v>
+        <v>705</v>
       </c>
       <c r="Q3" t="n">
-        <v>1732</v>
+        <v>218</v>
       </c>
       <c r="R3" t="n">
-        <v>5102</v>
+        <v>923</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1273553431</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273553431</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,52 +760,56 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>1986피트니스 헬스PT 24시 가양점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>1986fitness0@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>0507-1314-5607</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>https://blog.naver.com/1986fitness0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40uyc</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>705</v>
+        <v>1637</v>
       </c>
       <c r="Q4" t="n">
-        <v>218</v>
+        <v>1186</v>
       </c>
       <c r="R4" t="n">
-        <v>923</v>
+        <v>2823</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>37769368</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/37769368</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 24시 가양점</t>
+          <t>에이블짐 신방화역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1986fitness0@naver.com</t>
+          <t>ablegym14@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-5607</t>
+          <t>0507-1411-7984</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
+          <t>서울 강서구 방화대로 294 W타워 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness0</t>
+          <t>https://blog.naver.com/ablegym14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44b2e</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1637</v>
+        <v>1468</v>
       </c>
       <c r="Q5" t="n">
-        <v>1186</v>
+        <v>549</v>
       </c>
       <c r="R5" t="n">
-        <v>2823</v>
+        <v>2017</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37769368</t>
+          <t>1436688442</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37769368</t>
+          <t>https://m.place.naver.com/place/1436688442</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에이블짐 신방화역점</t>
+          <t>바디프로짐 PT 헬스 가양점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ablegym14@naver.com</t>
+          <t>bodyprogym2_gayang@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1411-7984</t>
+          <t>0507-1391-7831</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 방화대로 294 W타워 10층</t>
+          <t>서울 강서구 화곡로68길 3 영스퀘어 7층 바디프로짐 가양점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym14</t>
+          <t>https://www.instagram.com/bodyprogym2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -981,15 +993,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d7p6</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1468</v>
+        <v>1046</v>
       </c>
       <c r="Q6" t="n">
-        <v>549</v>
+        <v>997</v>
       </c>
       <c r="R6" t="n">
-        <v>2017</v>
+        <v>2043</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1436688442</t>
+          <t>1361992477</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1436688442</t>
+          <t>https://m.place.naver.com/place/1361992477</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1033,34 +1049,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디프로짐 PT 헬스 가양점</t>
+          <t>바디채널 화곡점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyprogym2_gayang@naver.com</t>
+          <t>bodychannel04@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1391-7831</t>
+          <t>0507-1314-2035</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로68길 3 영스퀘어 7층 바디프로짐 가양점</t>
+          <t>서울 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyprogym2</t>
+          <t>https://blog.naver.com/bodychannel04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o37o</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1046</v>
+        <v>442</v>
       </c>
       <c r="Q7" t="n">
-        <v>997</v>
+        <v>2212</v>
       </c>
       <c r="R7" t="n">
-        <v>2043</v>
+        <v>2654</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1361992477</t>
+          <t>1213490853</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1361992477</t>
+          <t>https://m.place.naver.com/place/1213490853</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,34 +1152,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>운동으로우주정복PT</t>
+          <t>버핏그라운드 PT 마곡 원그로브</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unujeong2023@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1341-9365</t>
+          <t>0507-1394-3687</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙로 161-8 에이동 2층 201,202호</t>
+          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unujeong2023</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1174,13 +1198,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmjt3l5</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>314</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>417</v>
+        <v>18</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1232,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1432557076</t>
+          <t>2084897715</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1432557076</t>
+          <t>https://m.place.naver.com/place/2084897715</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,33 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 마곡 원그로브</t>
+          <t>휘트니스피플 우먼 화곡역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1399-3624</t>
+          <t>02-2602-3912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
+          <t>서울 강서구 화곡로 153 광유빌딩 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1272,13 +1296,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w469ig</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>943</v>
+        <v>1309</v>
       </c>
       <c r="Q9" t="n">
-        <v>143</v>
+        <v>1495</v>
       </c>
       <c r="R9" t="n">
-        <v>1086</v>
+        <v>2804</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2038453115</t>
+          <t>1818807982</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038453115</t>
+          <t>https://m.place.naver.com/place/1818807982</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,29 +1352,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디채널 화곡점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodychannel04@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1314-2035</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
+          <t>서울 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannel04</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1366,10 +1394,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzwkzkx</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>442</v>
+        <v>77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2212</v>
+        <v>223</v>
       </c>
       <c r="R10" t="n">
-        <v>2654</v>
+        <v>300</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1213490853</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213490853</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,33 +1450,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 마곡 원그로브</t>
+          <t>바디채널 짐그라운드 등촌점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bodychannel15@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1394-3687</t>
+          <t>0507-1397-8868</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
+          <t>서울 강서구 공항대로 525 비원오피스텔 15층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://www.bodychannel.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1469,12 +1497,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmjt3l5</t>
+          <t>https://talk.naver.com/ct/w5taw1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1483,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>454</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1928</v>
       </c>
       <c r="R11" t="n">
-        <v>18</v>
+        <v>2382</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,109 +1526,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2084897715</t>
+          <t>1857550136</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084897715</t>
+          <t>https://m.place.naver.com/place/1857550136</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>휘트니스피플 우먼 화곡역점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>02-2602-3912</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1309</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1495</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2804</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1818807982</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1818807982</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 마곡나루지점</t>
+          <t>오리진휘트니스 발산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym5@naver.com</t>
+          <t>originfitness-@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>070-8670-8894</t>
+          <t>0507-1466-0937</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
+          <t>서울특별시 강서구 화곡로63길 93 지하1층 B01~B03호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym5</t>
+          <t>https://open.kakao.com/o/sWUvGJMh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3372</v>
+        <v>475</v>
       </c>
       <c r="Q2" t="n">
-        <v>1732</v>
+        <v>1778</v>
       </c>
       <c r="R2" t="n">
-        <v>5104</v>
+        <v>2253</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1273553431</t>
+          <t>1229648516</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273553431</t>
+          <t>https://m.place.naver.com/place/1229648516</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -658,44 +658,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>에이블짐 마곡나루지점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>ablegym5@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>070-8670-8894</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>https://blog.naver.com/ablegym5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>706</v>
+        <v>3372</v>
       </c>
       <c r="Q3" t="n">
-        <v>218</v>
+        <v>1732</v>
       </c>
       <c r="R3" t="n">
-        <v>924</v>
+        <v>5104</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>1273553431</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/1273553431</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,44 +752,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 24시 가양점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1986fitness0@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-5607</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
+          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness0</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1639</v>
+        <v>706</v>
       </c>
       <c r="Q4" t="n">
-        <v>1186</v>
+        <v>218</v>
       </c>
       <c r="R4" t="n">
-        <v>2825</v>
+        <v>924</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>37769368</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37769368</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이블짐 신방화역점</t>
+          <t>1986피트니스 헬스PT 24시 가양점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ablegym14@naver.com</t>
+          <t>1986fitness0@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1411-7984</t>
+          <t>0507-1314-5607</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 방화대로 294 W타워 10층</t>
+          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym14</t>
+          <t>https://blog.naver.com/1986fitness0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1470</v>
+        <v>1639</v>
       </c>
       <c r="Q5" t="n">
-        <v>549</v>
+        <v>1186</v>
       </c>
       <c r="R5" t="n">
-        <v>2019</v>
+        <v>2825</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1436688442</t>
+          <t>37769368</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1436688442</t>
+          <t>https://m.place.naver.com/place/37769368</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지컬스토리 PT</t>
+          <t>에이블짐 신방화역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hjs2168@naver.com</t>
+          <t>ablegym14@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1366-5303</t>
+          <t>0507-1411-7984</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로77길 13 3층</t>
+          <t>서울특별시 강서구 방화대로 294 W타워 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/physical.story</t>
+          <t>https://blog.naver.com/ablegym14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>161</v>
+        <v>1470</v>
       </c>
       <c r="Q6" t="n">
-        <v>125</v>
+        <v>549</v>
       </c>
       <c r="R6" t="n">
-        <v>286</v>
+        <v>2019</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1292115406</t>
+          <t>1436688442</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1292115406</t>
+          <t>https://m.place.naver.com/place/1436688442</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>피지컬스토리 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>hjs2168@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1366-5303</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 양천로77길 13 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://www.instagram.com/physical.story</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="Q7" t="n">
-        <v>223</v>
+        <v>125</v>
       </c>
       <c r="R7" t="n">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1292115406</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1292115406</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바디채널 화곡2호점</t>
+          <t>버핏그라운드 마곡 원그로브</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bodygymmm@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1409-2606</t>
+          <t>0507-1399-3624</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 곰달래로 198 2층</t>
+          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodygymmm</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>75</v>
+        <v>943</v>
       </c>
       <c r="Q8" t="n">
-        <v>297</v>
+        <v>143</v>
       </c>
       <c r="R8" t="n">
-        <v>372</v>
+        <v>1086</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,56 +1204,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1348945802</t>
+          <t>2038453115</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348945802</t>
+          <t>https://m.place.naver.com/place/2038453115</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>껀바디 PT&amp;필라테스</t>
+          <t>바디채널 화곡점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kkunbody@naver.com</t>
+          <t>bodychannel04@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1329-8356</t>
+          <t>0507-1314-2035</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
+          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
+          <t>https://blog.naver.com/bodychannel04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>95</v>
+        <v>442</v>
       </c>
       <c r="Q9" t="n">
-        <v>271</v>
+        <v>2209</v>
       </c>
       <c r="R9" t="n">
-        <v>366</v>
+        <v>2651</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1200267493</t>
+          <t>1213490853</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200267493</t>
+          <t>https://m.place.naver.com/place/1213490853</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포애니 우장산역점</t>
+          <t>휘트니스피플 우먼 화곡역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>spoany93@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1308-8802</t>
+          <t>02-2602-3912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 267 송화쇼핑센터 9층</t>
+          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA4</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1070</v>
+        <v>1309</v>
       </c>
       <c r="Q10" t="n">
-        <v>1562</v>
+        <v>1495</v>
       </c>
       <c r="R10" t="n">
-        <v>2632</v>
+        <v>2804</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1893634711</t>
+          <t>1818807982</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893634711</t>
+          <t>https://m.place.naver.com/place/1818807982</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하이짐 PT 까치산점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>higym012@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1478-1366</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 61 영상빌딩 5층 하이짐</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym012</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="n">
-        <v>313</v>
+        <v>223</v>
       </c>
       <c r="R11" t="n">
-        <v>615</v>
+        <v>300</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1486,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38547689</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38547689</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>피티하모니 강서구청점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>tuvasmedetruire0@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1355-2365</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 강서구 화곡로 339 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tuvasmedetruire0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>26</v>
+      </c>
+      <c r="R12" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2082352683</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082352683</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>오리진휘트니스 발산점</t>
+          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>originfitness-@naver.com</t>
+          <t>poha0092@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1466-0937</t>
+          <t>0507-1389-0198</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로63길 93 지하1층 B01~B03호</t>
+          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sWUvGJMh</t>
+          <t>https://blog.naver.com/poha0092</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="Q2" t="n">
-        <v>1778</v>
+        <v>645</v>
       </c>
       <c r="R2" t="n">
-        <v>2253</v>
+        <v>1071</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1229648516</t>
+          <t>1208400007</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229648516</t>
+          <t>https://m.place.naver.com/place/1208400007</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피지컬스토리 PT</t>
+          <t>여성전문 PT 헬스 바이브먼트</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hjs2168@naver.com</t>
+          <t>vibement_magok@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1366-5303</t>
+          <t>0507-1471-4007</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로77길 13 3층</t>
+          <t>서울특별시 강서구 공항대로 212 B동 4층 405호~ 407호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/physical.story</t>
+          <t>https://blog.naver.com/vibement_magok</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>161</v>
+        <v>373</v>
       </c>
       <c r="Q7" t="n">
-        <v>125</v>
+        <v>2200</v>
       </c>
       <c r="R7" t="n">
-        <v>286</v>
+        <v>2573</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1292115406</t>
+          <t>1814620278</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1292115406</t>
+          <t>https://m.place.naver.com/place/1814620278</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,38 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 마곡 원그로브</t>
+          <t>팀버핏 마곡 원그로브</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>dkgus7225@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1399-3624</t>
+          <t>0507-1420-3624</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
+          <t>서울특별시 강서구 공항대로 165 C동 지상 1층 W119호~125호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://teambutfit.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1169,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1180,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>943</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="n">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
-        <v>1086</v>
+        <v>126</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2038453115</t>
+          <t>2040321945</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038453115</t>
+          <t>https://m.place.naver.com/place/2040321945</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1315,39 +1311,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 화곡역점</t>
+          <t>버핏그라운드 PT 마곡 원그로브</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-2602-3912</t>
+          <t>0507-1394-3687</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
+          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1362,13 +1362,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmjt3l5</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1309</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1495</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>2804</v>
+        <v>18</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1818807982</t>
+          <t>2084897715</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1818807982</t>
+          <t>https://m.place.naver.com/place/2084897715</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>휘트니스피플 우먼 화곡역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>02-2602-3912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>77</v>
+        <v>1309</v>
       </c>
       <c r="Q11" t="n">
-        <v>223</v>
+        <v>1495</v>
       </c>
       <c r="R11" t="n">
-        <v>300</v>
+        <v>2804</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1818807982</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1818807982</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1503,34 +1507,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피티하모니 강서구청점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tuvasmedetruire0@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1355-2365</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 339 5층</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tuvasmedetruire0</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1565,13 +1569,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>223</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,12 +1584,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2082352683</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082352683</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
+          <t>랩스휘트니스 까치산점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>poha0092@naver.com</t>
+          <t>rapsfit11@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1389-0198</t>
+          <t>0507-1484-6681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
+          <t>서울특별시 강서구 강서로 27 8층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/poha0092</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,23 +596,27 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0t2s</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>426</v>
+        <v>813</v>
       </c>
       <c r="Q2" t="n">
-        <v>645</v>
+        <v>1991</v>
       </c>
       <c r="R2" t="n">
-        <v>1071</v>
+        <v>2804</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1208400007</t>
+          <t>1579879801</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208400007</t>
+          <t>https://m.place.naver.com/place/1579879801</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gb51</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3372</v>
+        <v>3377</v>
       </c>
       <c r="Q3" t="n">
         <v>1732</v>
       </c>
       <c r="R3" t="n">
-        <v>5104</v>
+        <v>5109</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -752,44 +760,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>1986피트니스 헬스PT 24시 가양점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>1986fitness0@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>0507-1314-5607</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>https://blog.naver.com/1986fitness0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>706</v>
+        <v>1639</v>
       </c>
       <c r="Q4" t="n">
-        <v>218</v>
+        <v>1188</v>
       </c>
       <c r="R4" t="n">
-        <v>924</v>
+        <v>2827</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>37769368</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/37769368</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,44 +854,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 24시 가양점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1986fitness0@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-5607</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로 500 노블리움오피스텔 307호, 308호</t>
+          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness0</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1639</v>
+        <v>706</v>
       </c>
       <c r="Q5" t="n">
-        <v>1186</v>
+        <v>218</v>
       </c>
       <c r="R5" t="n">
-        <v>2825</v>
+        <v>924</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37769368</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37769368</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1034,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여성전문 PT 헬스 바이브먼트</t>
+          <t>피지컬스토리 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>vibement_magok@naver.com</t>
+          <t>hjs2168@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1471-4007</t>
+          <t>0507-1366-5303</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 212 B동 4층 405호~ 407호</t>
+          <t>서울특별시 강서구 양천로77길 13 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vibement_magok</t>
+          <t>https://www.instagram.com/physical.story</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1079,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>373</v>
+        <v>161</v>
       </c>
       <c r="Q7" t="n">
-        <v>2200</v>
+        <v>125</v>
       </c>
       <c r="R7" t="n">
-        <v>2573</v>
+        <v>286</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1814620278</t>
+          <t>1292115406</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814620278</t>
+          <t>https://m.place.naver.com/place/1292115406</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,34 +1136,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀버핏 마곡 원그로브</t>
+          <t>휘트니스피플 우먼 화곡역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dkgus7225@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1420-3624</t>
+          <t>02-2602-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 165 C동 지상 1층 W119호~125호</t>
+          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://teambutfit.com</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1173,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>96</v>
+        <v>1311</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>1495</v>
       </c>
       <c r="R8" t="n">
-        <v>126</v>
+        <v>2806</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2040321945</t>
+          <t>1818807982</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040321945</t>
+          <t>https://m.place.naver.com/place/1818807982</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디채널 화곡점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodychannel04@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-2035</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannel04</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2209</v>
+        <v>223</v>
       </c>
       <c r="R9" t="n">
-        <v>2651</v>
+        <v>301</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1213490853</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213490853</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,43 +1319,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 마곡 원그로브</t>
+          <t>바디채널 화곡2호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bodygymmm@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1394-3687</t>
+          <t>0507-1409-2606</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
+          <t>서울특별시 강서구 곰달래로 198 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/bodygymmm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1362,17 +1366,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmjt3l5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>297</v>
       </c>
       <c r="R10" t="n">
-        <v>18</v>
+        <v>372</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2084897715</t>
+          <t>1348945802</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084897715</t>
+          <t>https://m.place.naver.com/place/1348945802</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 화곡역점</t>
+          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>poha0092@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02-2602-3912</t>
+          <t>0507-1389-0198</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
+          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/poha0092</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1309</v>
+        <v>431</v>
       </c>
       <c r="Q11" t="n">
-        <v>1495</v>
+        <v>646</v>
       </c>
       <c r="R11" t="n">
-        <v>2804</v>
+        <v>1077</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1818807982</t>
+          <t>1208400007</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1818807982</t>
+          <t>https://m.place.naver.com/place/1208400007</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1507,39 +1507,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>껀바디 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>kkunbody@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1329-8356</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="R12" t="n">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1200267493</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1200267493</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>랩스휘트니스 까치산점 헬스 PT</t>
+          <t>무궁화체육관 PT&amp; Pila 등촌점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rapsfit11@naver.com</t>
+          <t>mugunghwa-gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1484-6681</t>
+          <t>0507-1443-9683</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 27 8층</t>
+          <t>서울특별시 강서구 화곡로66길 76 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mugunghwa-gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,27 +596,23 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc0t2s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>813</v>
+        <v>96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1991</v>
+        <v>338</v>
       </c>
       <c r="R2" t="n">
-        <v>2804</v>
+        <v>434</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1579879801</t>
+          <t>1983043639</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579879801</t>
+          <t>https://m.place.naver.com/place/1983043639</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ablegym5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4gb51</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3377</v>
+        <v>3383</v>
       </c>
       <c r="Q3" t="n">
         <v>1732</v>
       </c>
       <c r="R3" t="n">
-        <v>5109</v>
+        <v>5115</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="Q4" t="n">
         <v>1188</v>
       </c>
       <c r="R4" t="n">
-        <v>2827</v>
+        <v>2828</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -936,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1136,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 화곡역점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-2602-3912</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로 153 광유빌딩 6층</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1311</v>
+        <v>78</v>
       </c>
       <c r="Q8" t="n">
-        <v>1495</v>
+        <v>223</v>
       </c>
       <c r="R8" t="n">
-        <v>2806</v>
+        <v>301</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1818807982</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1818807982</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1230,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>좋은습관 PT 헬스 까치산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
+          <t>kyyy_y@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1472-1627</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 강서로7길 85 2층 좋은습관 PT STUDIO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://trial.todayhabit.co.kr/experience?studioId=18&amp;isSkipError=false</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1267,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="Q9" t="n">
-        <v>223</v>
+        <v>349</v>
       </c>
       <c r="R9" t="n">
-        <v>301</v>
+        <v>653</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>1952728394</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/1952728394</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디채널 화곡2호점</t>
+          <t>헬스보이짐 골프인 양천향교역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodygymmm@naver.com</t>
+          <t>healthboy76@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1409-2606</t>
+          <t>0507-1449-7777</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 곰달래로 198 2층</t>
+          <t>서울특별시 강서구 마곡동로10길 23 마곡대방디엠시티 2차, 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodygymmm</t>
+          <t>https://www.instagram.com/healthboy76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1361,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1381,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>75</v>
+        <v>1350</v>
       </c>
       <c r="Q10" t="n">
-        <v>297</v>
+        <v>938</v>
       </c>
       <c r="R10" t="n">
-        <v>372</v>
+        <v>2288</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1348945802</t>
+          <t>1825654296</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348945802</t>
+          <t>https://m.place.naver.com/place/1825654296</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
+          <t>스포애니 우장산역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>poha0092@naver.com</t>
+          <t>spoany93@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1389-0198</t>
+          <t>0507-1308-8802</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
+          <t>서울특별시 강서구 강서로 267 송화쇼핑센터 9층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/poha0092</t>
+          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1475,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>431</v>
+        <v>1071</v>
       </c>
       <c r="Q11" t="n">
-        <v>646</v>
+        <v>1566</v>
       </c>
       <c r="R11" t="n">
-        <v>1077</v>
+        <v>2637</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1208400007</t>
+          <t>1893634711</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208400007</t>
+          <t>https://m.place.naver.com/place/1893634711</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1512,34 +1504,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>껀바디 PT&amp;필라테스</t>
+          <t>하이짐 PT 까치산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kkunbody@naver.com</t>
+          <t>higym012@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1329-8356</t>
+          <t>0507-1478-1366</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
+          <t>서울특별시 강서구 강서로 61 영상빌딩 5층 하이짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
+          <t>https://blog.naver.com/higym012</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1549,7 +1541,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1569,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="Q12" t="n">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="R12" t="n">
-        <v>366</v>
+        <v>615</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1200267493</t>
+          <t>38547689</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200267493</t>
+          <t>https://m.place.naver.com/place/38547689</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>무궁화체육관 PT&amp; Pila 등촌점</t>
+          <t>랩스휘트니스 까치산점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mugunghwa-gym@naver.com</t>
+          <t>rapsfit11@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1443-9683</t>
+          <t>0507-1484-6681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 화곡로66길 76 4층</t>
+          <t>서울특별시 강서구 강서로 27 8층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mugunghwa-gym</t>
+          <t>https://blog.naver.com/rapsfit11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>96</v>
+        <v>814</v>
       </c>
       <c r="Q2" t="n">
-        <v>338</v>
+        <v>1995</v>
       </c>
       <c r="R2" t="n">
-        <v>434</v>
+        <v>2809</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1983043639</t>
+          <t>1579879801</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983043639</t>
+          <t>https://m.place.naver.com/place/1579879801</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,44 +658,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 마곡나루지점</t>
+          <t>에이블짐 등촌역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym5@naver.com</t>
+          <t>ablegym41@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-8670-8894</t>
+          <t>0507-1495-0428</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
+          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym5</t>
+          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3383</v>
+        <v>706</v>
       </c>
       <c r="Q3" t="n">
-        <v>1732</v>
+        <v>215</v>
       </c>
       <c r="R3" t="n">
-        <v>5115</v>
+        <v>921</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1273553431</t>
+          <t>1579729656</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1273553431</t>
+          <t>https://m.place.naver.com/place/1579729656</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="Q4" t="n">
         <v>1188</v>
       </c>
       <c r="R4" t="n">
-        <v>2828</v>
+        <v>2830</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,44 +846,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에이블짐 등촌역점</t>
+          <t>에이블짐 마곡나루지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ablegym41@naver.com</t>
+          <t>ablegym5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1495-0428</t>
+          <t>070-8670-8894</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 공항대로 543 지하 1층</t>
+          <t>서울특별시 강서구 마곡중앙로 161-17 보타닉파크타워 1차 12층 에이블짐 마곡나루점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1055308</t>
+          <t>https://blog.naver.com/ablegym5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>706</v>
+        <v>3383</v>
       </c>
       <c r="Q5" t="n">
-        <v>218</v>
+        <v>1732</v>
       </c>
       <c r="R5" t="n">
-        <v>924</v>
+        <v>5115</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1579729656</t>
+          <t>1273553431</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579729656</t>
+          <t>https://m.place.naver.com/place/1273553431</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피지컬스토리 PT</t>
+          <t>바디프로짐 PT 헬스 가양점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hjs2168@naver.com</t>
+          <t>bodyprogym2_gayang@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1366-5303</t>
+          <t>0507-1391-7831</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 양천로77길 13 3층</t>
+          <t>서울특별시 강서구 화곡로68길 3 영스퀘어 7층 바디프로짐 가양점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/physical.story</t>
+          <t>https://www.instagram.com/bodyprogym2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>161</v>
+        <v>1046</v>
       </c>
       <c r="Q7" t="n">
-        <v>125</v>
+        <v>997</v>
       </c>
       <c r="R7" t="n">
-        <v>286</v>
+        <v>2043</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1292115406</t>
+          <t>1361992477</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1292115406</t>
+          <t>https://m.place.naver.com/place/1361992477</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1123,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>버핏그라운드 PT 마곡 원그로브</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1394-3687</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1170,13 +1174,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmjt3l5</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>223</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>301</v>
+        <v>18</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>2084897715</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/2084897715</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,34 +1230,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>좋은습관 PT 헬스 까치산점</t>
+          <t>나무 EMS스파&amp;운동 마곡점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kyyy_y@naver.com</t>
+          <t>goforit_20_@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1472-1627</t>
+          <t>02-6080-2096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로7길 85 2층 좋은습관 PT STUDIO</t>
+          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://trial.todayhabit.co.kr/experience?studioId=18&amp;isSkipError=false</t>
+          <t>https://blog.naver.com/goforit_20_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1267,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1283,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="n">
-        <v>349</v>
+        <v>223</v>
       </c>
       <c r="R9" t="n">
-        <v>653</v>
+        <v>302</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1952728394</t>
+          <t>1611015705</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1952728394</t>
+          <t>https://m.place.naver.com/place/1611015705</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 양천향교역점</t>
+          <t>바디채널 화곡2호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>healthboy76@naver.com</t>
+          <t>bodygymmm@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1449-7777</t>
+          <t>0507-1409-2606</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡동로10길 23 마곡대방디엠시티 2차, 2층</t>
+          <t>서울특별시 강서구 곰달래로 198 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthboy76</t>
+          <t>https://blog.naver.com/bodygymmm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1361,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1350</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>938</v>
+        <v>297</v>
       </c>
       <c r="R10" t="n">
-        <v>2288</v>
+        <v>371</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1825654296</t>
+          <t>1348945802</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1825654296</t>
+          <t>https://m.place.naver.com/place/1348945802</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스포애니 우장산역점</t>
+          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>spoany93@naver.com</t>
+          <t>poha0092@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1308-8802</t>
+          <t>0507-1389-0198</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 267 송화쇼핑센터 9층</t>
+          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://m.spoany.co.kr/branch/branch_detail.html?base_seq=MTA4</t>
+          <t>https://blog.naver.com/poha0092</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1455,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1071</v>
+        <v>432</v>
       </c>
       <c r="Q11" t="n">
-        <v>1566</v>
+        <v>655</v>
       </c>
       <c r="R11" t="n">
-        <v>2637</v>
+        <v>1087</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1893634711</t>
+          <t>1208400007</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893634711</t>
+          <t>https://m.place.naver.com/place/1208400007</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,34 +1512,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하이짐 PT 까치산점</t>
+          <t>껀바디 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>higym012@naver.com</t>
+          <t>kkunbody@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1478-1366</t>
+          <t>0507-1329-8356</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 61 영상빌딩 5층 하이짐</t>
+          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higym012</t>
+          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1541,7 +1549,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,13 +1569,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>302</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="R12" t="n">
-        <v>615</v>
+        <v>367</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1584,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>38547689</t>
+          <t>1200267493</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38547689</t>
+          <t>https://m.place.naver.com/place/1200267493</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/강서_PT.xlsx
+++ b/naver-place-crawler/results_health/강서_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>랩스휘트니스 까치산점 헬스 PT</t>
+          <t>오리진휘트니스 발산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rapsfit11@naver.com</t>
+          <t>originfitness-@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1484-6681</t>
+          <t>0507-1466-0937</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 27 8층</t>
+          <t>서울특별시 강서구 화곡로63길 93 지하1층 B01~B03호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit11</t>
+          <t>https://open.kakao.com/o/sWUvGJMh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>814</v>
+        <v>480</v>
       </c>
       <c r="Q2" t="n">
-        <v>1995</v>
+        <v>1777</v>
       </c>
       <c r="R2" t="n">
-        <v>2809</v>
+        <v>2257</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1579879801</t>
+          <t>1229648516</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579879801</t>
+          <t>https://m.place.naver.com/place/1229648516</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -812,10 +812,10 @@
         <v>1642</v>
       </c>
       <c r="Q4" t="n">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="R4" t="n">
-        <v>2830</v>
+        <v>2831</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3383</v>
+        <v>3385</v>
       </c>
       <c r="Q5" t="n">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="R5" t="n">
-        <v>5115</v>
+        <v>5119</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1128,38 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 마곡 원그로브</t>
+          <t>운동으로우주정복PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>unujeong2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1394-3687</t>
+          <t>0507-1341-9365</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 강서구 공항대로 165 원그로브 C동 1층 버핏그라운드</t>
+          <t>서울특별시 강서구 마곡중앙로 161-8 에이동 2층 201,202호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/unujeong2023</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1174,17 +1170,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmjt3l5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>314</v>
       </c>
       <c r="R8" t="n">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2084897715</t>
+          <t>1432557076</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084897715</t>
+          <t>https://m.place.naver.com/place/1432557076</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1222,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>나무 EMS스파&amp;운동 마곡점</t>
+          <t>버핏그라운드 마곡 원그로브</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goforit_20_@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-6080-2096</t>
+          <t>0507-1399-3624</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 마곡중앙6로 21 이너매스마곡1차 3층 318호~319호</t>
+          <t>서울특별시 강서구 공항대로 165 원그로브 C동 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goforit_20_</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>943</v>
       </c>
       <c r="Q9" t="n">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c r="R9" t="n">
-        <v>302</v>
+        <v>1087</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,56 +1298,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1611015705</t>
+          <t>2038453115</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611015705</t>
+          <t>https://m.place.naver.com/place/2038453115</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디채널 화곡2호점</t>
+          <t>같이운동 화곡역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodygymmm@naver.com</t>
+          <t>edenfitt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1409-2606</t>
+          <t>0507-1381-1129</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 곰달래로 198 2층</t>
+          <t>서울특별시 강서구 화곡로 176 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodygymmm</t>
+          <t>https://togethertraining.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1372,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>442</v>
       </c>
       <c r="Q10" t="n">
-        <v>297</v>
+        <v>498</v>
       </c>
       <c r="R10" t="n">
-        <v>371</v>
+        <v>940</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1348945802</t>
+          <t>1156492601</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1348945802</t>
+          <t>https://m.place.naver.com/place/1156492601</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>밸런스22짐 헬스&amp;PT 화곡점</t>
+          <t>바디채널 화곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>poha0092@naver.com</t>
+          <t>bodychannel04@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1389-0198</t>
+          <t>0507-1314-2035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 강서구 강서로 199 2층, 3층</t>
+          <t>서울특별시 강서구 까치산로4길 3 바디채널 화곡역점 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/poha0092</t>
+          <t>https://blog.naver.com/bodychannel04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="Q11" t="n">
-        <v>655</v>
+        <v>2211</v>
       </c>
       <c r="R11" t="n">
-        <v>1087</v>
+        <v>2653</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,111 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1208400007</t>
+          <t>1213490853</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208400007</t>
+          <t>https://m.place.naver.com/place/1213490853</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>껀바디 PT&amp;필라테스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kkunbody@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1329-8356</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 강서구 공항대로 247 C동 331호, 332호, 333호, 410호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://litt.ly/kkun_body?fbclid=PAAab7C5rUQ4wY5wOwgpY3nwVf5NI9vSdrwMN3sJWlCSqYQjTe3614QbRlGQA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>272</v>
-      </c>
-      <c r="R12" t="n">
-        <v>367</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1200267493</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1200267493</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
